--- a/data/cost_noise.xlsx
+++ b/data/cost_noise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1399C210-C219-43F6-9C8B-5B6844EDF16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629FE6C6-46C0-46D1-A1F8-C8E96221EF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="yearly" sheetId="1" r:id="rId1"/>
@@ -445,14 +445,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,88 +466,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>43.977855361596006</v>
+        <v>45.059750623441403</v>
       </c>
       <c r="C2" s="2">
-        <v>6.4673316708229418</v>
+        <v>6.6264339152119707</v>
       </c>
       <c r="D2" s="2">
-        <v>50.44518703241895</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51.686184538653372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>87.955710723192013</v>
+        <v>90.119501246882805</v>
       </c>
       <c r="C3" s="2">
-        <v>7.7607980049875307</v>
+        <v>7.9517206982543653</v>
       </c>
       <c r="D3" s="2">
-        <v>95.716508728179548</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98.071221945137168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>87.955710723192013</v>
+        <v>90.119501246882805</v>
       </c>
       <c r="C4" s="2">
-        <v>11.641197007481296</v>
+        <v>11.927581047381548</v>
       </c>
       <c r="D4" s="2">
-        <v>99.596907730673308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102.04708229426436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>166.8571571072319</v>
+        <v>170.96199501246886</v>
       </c>
       <c r="C5" s="2">
-        <v>15.521596009975061</v>
+        <v>15.903441396508731</v>
       </c>
       <c r="D5" s="2">
-        <v>182.37875311720697</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>186.86543640897759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>166.8571571072319</v>
+        <v>170.96199501246886</v>
       </c>
       <c r="C6" s="2">
-        <v>20.695461346633415</v>
+        <v>21.204588528678308</v>
       </c>
       <c r="D6" s="2">
-        <v>187.55261845386534</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192.16658354114716</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>166.8571571072319</v>
+        <v>170.96199501246886</v>
       </c>
       <c r="C7" s="2">
-        <v>27.162793017456359</v>
+        <v>27.83102244389028</v>
       </c>
       <c r="D7" s="2">
-        <v>194.01995012468828</v>
+        <v>198.79301745635914</v>
       </c>
     </row>
   </sheetData>
@@ -559,15 +559,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF4BF86-65E5-4200-9072-ED7C30D056BE}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -587,64 +587,64 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="2">
-        <v>1.0865117206982542</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="C2" s="2">
-        <v>332.42084788029922</v>
+        <v>341</v>
       </c>
       <c r="D2" s="2">
-        <v>2.6516059850374063</v>
+        <v>2.72</v>
       </c>
       <c r="E2" s="2">
-        <v>11.692935660847878</v>
+        <v>11.98</v>
       </c>
       <c r="F2" s="1">
-        <v>0.59499451371571066</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>1.0865117206982542</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>332.42084788029922</v>
+        <v>341</v>
       </c>
       <c r="D3" s="2">
-        <v>2.6516059850374063</v>
+        <v>2.72</v>
       </c>
       <c r="E3" s="2">
-        <v>11.692935660847878</v>
+        <v>11.98</v>
       </c>
       <c r="F3" s="1">
-        <v>0.14228129675810472</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="2">
-        <v>1.0865117206982542</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="C4" s="2">
-        <v>332.42084788029922</v>
+        <v>341</v>
       </c>
       <c r="D4" s="2">
-        <v>2.6516059850374063</v>
+        <v>2.72</v>
       </c>
       <c r="E4" s="2">
-        <v>11.692935660847878</v>
+        <v>11.98</v>
       </c>
       <c r="F4" s="1">
-        <v>1.2934663341645884E-2</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94DDE2AB-6DB2-485B-9D60-C39619DF6270}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -672,92 +672,92 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2">
-        <v>23.641086328022151</v>
+        <v>25.216479618329071</v>
       </c>
       <c r="C2" s="2">
-        <v>57.424046467753122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61.250666626080658</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2">
-        <v>58.612395707146824</v>
+        <v>62.518205010689861</v>
       </c>
       <c r="C3" s="2">
-        <v>79.099569076181183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84.370601407765648</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="2">
-        <v>74.204185475430393</v>
+        <v>79.148999528755809</v>
       </c>
       <c r="C4" s="2">
-        <v>100.77509168460976</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107.49053618945122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="2">
-        <v>95.819728401863671</v>
+        <v>102.204957706001</v>
       </c>
       <c r="C5" s="2">
-        <v>122.45061429303937</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130.61047097113786</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="2">
-        <v>120.859074449839</v>
+        <v>128.91287419149032</v>
       </c>
       <c r="C6" s="2">
-        <v>144.12613690146694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153.73040575282232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="2">
-        <v>146.83230703511626</v>
+        <v>156.61690948924382</v>
       </c>
       <c r="C7" s="2">
-        <v>144.12613690146694</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153.73040575282232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="2">
-        <v>173.73973189799972</v>
+        <v>185.31738971346994</v>
       </c>
       <c r="C8" s="2">
-        <v>144.12613690146694</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153.73040575282232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="2">
-        <v>188.81741016031719</v>
+        <v>201.39981339392443</v>
       </c>
       <c r="C9" s="2">
-        <v>144.12613690146694</v>
+        <v>153.73040575282232</v>
       </c>
     </row>
   </sheetData>
